--- a/artfynd/A 21799-2025 artfynd.xlsx
+++ b/artfynd/A 21799-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128349850</v>
       </c>
       <c r="B2" t="n">
-        <v>97352</v>
+        <v>97357</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
         <v>128349908</v>
       </c>
       <c r="B3" t="n">
-        <v>96075</v>
+        <v>96080</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 21799-2025 artfynd.xlsx
+++ b/artfynd/A 21799-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128349850</v>
       </c>
       <c r="B2" t="n">
-        <v>97357</v>
+        <v>97450</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
         <v>128349908</v>
       </c>
       <c r="B3" t="n">
-        <v>96080</v>
+        <v>96173</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 21799-2025 artfynd.xlsx
+++ b/artfynd/A 21799-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128349850</v>
       </c>
       <c r="B2" t="n">
-        <v>97450</v>
+        <v>97462</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
         <v>128349908</v>
       </c>
       <c r="B3" t="n">
-        <v>96173</v>
+        <v>96185</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 21799-2025 artfynd.xlsx
+++ b/artfynd/A 21799-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128349850</v>
       </c>
       <c r="B2" t="n">
-        <v>97462</v>
+        <v>97464</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
         <v>128349908</v>
       </c>
       <c r="B3" t="n">
-        <v>96185</v>
+        <v>96187</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 21799-2025 artfynd.xlsx
+++ b/artfynd/A 21799-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128349850</v>
       </c>
       <c r="B2" t="n">
-        <v>97464</v>
+        <v>97465</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
         <v>128349908</v>
       </c>
       <c r="B3" t="n">
-        <v>96187</v>
+        <v>96188</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 21799-2025 artfynd.xlsx
+++ b/artfynd/A 21799-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128349850</v>
       </c>
       <c r="B2" t="n">
-        <v>97465</v>
+        <v>97492</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
         <v>128349908</v>
       </c>
       <c r="B3" t="n">
-        <v>96188</v>
+        <v>96215</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 21799-2025 artfynd.xlsx
+++ b/artfynd/A 21799-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128349850</v>
       </c>
       <c r="B2" t="n">
-        <v>97492</v>
+        <v>97505</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
         <v>128349908</v>
       </c>
       <c r="B3" t="n">
-        <v>96215</v>
+        <v>96228</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 21799-2025 artfynd.xlsx
+++ b/artfynd/A 21799-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128349850</v>
       </c>
       <c r="B2" t="n">
-        <v>97505</v>
+        <v>97509</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
         <v>128349908</v>
       </c>
       <c r="B3" t="n">
-        <v>96228</v>
+        <v>96232</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 21799-2025 artfynd.xlsx
+++ b/artfynd/A 21799-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128349850</v>
+        <v>128349908</v>
       </c>
       <c r="B2" t="n">
-        <v>97509</v>
+        <v>96708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,43 +686,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>224363</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vanlig revlummer</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. annotinum</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Svanviken, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>607999</v>
+        <v>607737</v>
       </c>
       <c r="R2" t="n">
-        <v>6480903</v>
+        <v>6480834</v>
       </c>
       <c r="S2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -751,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -761,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128349908</v>
+        <v>128349850</v>
       </c>
       <c r="B3" t="n">
-        <v>96232</v>
+        <v>97985</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -799,42 +798,43 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>224363</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vanlig revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Svanviken, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>607737</v>
+        <v>607999</v>
       </c>
       <c r="R3" t="n">
-        <v>6480834</v>
+        <v>6480903</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -863,7 +863,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 21799-2025 artfynd.xlsx
+++ b/artfynd/A 21799-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128349908</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -897,8 +907,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128349850</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>